--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ALABAMA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/ALABAMA_2016.xlsx
@@ -553,7 +553,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="12">
@@ -805,7 +805,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="26">
@@ -1003,7 +1003,7 @@
         <v>7</v>
       </c>
       <c r="D36">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="37">
@@ -1039,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="39">
@@ -1309,7 +1309,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="54">
@@ -1399,7 +1399,7 @@
         <v>7</v>
       </c>
       <c r="D58">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="59">
@@ -1651,7 +1651,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="73">
@@ -1939,7 +1939,7 @@
         <v>7</v>
       </c>
       <c r="D88">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="89">
@@ -2407,7 +2407,7 @@
         <v>7</v>
       </c>
       <c r="D114">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="115">
@@ -2803,7 +2803,7 @@
         <v>7</v>
       </c>
       <c r="D136">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="137">
@@ -2821,7 +2821,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="138">
@@ -2940,14 +2940,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C144">
         <v>7</v>
       </c>
       <c r="D144">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="145">
@@ -3199,7 +3199,7 @@
         <v>7</v>
       </c>
       <c r="D158">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="159">
@@ -3757,7 +3757,7 @@
         <v>7</v>
       </c>
       <c r="D189">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="190">
@@ -4819,7 +4819,7 @@
         <v>7</v>
       </c>
       <c r="D248">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="249">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C249">
@@ -4927,7 +4927,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="255">
@@ -5449,7 +5449,7 @@
         <v>7</v>
       </c>
       <c r="D283">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="284">
@@ -5791,7 +5791,7 @@
         <v>7</v>
       </c>
       <c r="D302">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="303">
@@ -7069,7 +7069,7 @@
         <v>7</v>
       </c>
       <c r="D373">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="374">
@@ -7141,7 +7141,7 @@
         <v>7</v>
       </c>
       <c r="D377">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="378">
@@ -7753,7 +7753,7 @@
         <v>7</v>
       </c>
       <c r="D411">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="412">
@@ -8329,7 +8329,7 @@
         <v>7</v>
       </c>
       <c r="D443">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="444">
@@ -9391,7 +9391,7 @@
         <v>7</v>
       </c>
       <c r="D502">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="503">
@@ -9787,7 +9787,7 @@
         <v>7</v>
       </c>
       <c r="D524">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="525">
@@ -9967,7 +9967,7 @@
         <v>7</v>
       </c>
       <c r="D534">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="535">
@@ -11857,7 +11857,7 @@
         <v>7</v>
       </c>
       <c r="D639">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="640">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C643">
@@ -12055,7 +12055,7 @@
         <v>7</v>
       </c>
       <c r="D650">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="651">
@@ -12253,7 +12253,7 @@
         <v>7</v>
       </c>
       <c r="D661">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="662">
@@ -14845,7 +14845,7 @@
         <v>7</v>
       </c>
       <c r="D805">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="806">
@@ -15439,7 +15439,7 @@
         <v>7</v>
       </c>
       <c r="D838">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="839">
@@ -15709,7 +15709,7 @@
         <v>7</v>
       </c>
       <c r="D853">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="854">
@@ -15889,7 +15889,7 @@
         <v>7</v>
       </c>
       <c r="D863">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="864">
@@ -16699,7 +16699,7 @@
         <v>7</v>
       </c>
       <c r="D908">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="909">
@@ -16915,7 +16915,7 @@
         <v>7</v>
       </c>
       <c r="D920">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="921">
@@ -17653,7 +17653,7 @@
         <v>7</v>
       </c>
       <c r="D961">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="962">
@@ -17707,7 +17707,7 @@
         <v>7</v>
       </c>
       <c r="D964">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="965">
@@ -18679,7 +18679,7 @@
         <v>7</v>
       </c>
       <c r="D1018">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="1019">
@@ -19417,7 +19417,7 @@
         <v>7</v>
       </c>
       <c r="D1059">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="1060">
@@ -19525,7 +19525,7 @@
         <v>7</v>
       </c>
       <c r="D1065">
-        <v>0.0009119332985930171</v>
+        <v>0.0009119332985930173</v>
       </c>
     </row>
     <row r="1066">
